--- a/data/delivery/mock/mock_project/早期介入/交付预案/输出结果/项目责任矩阵.xlsx
+++ b/data/delivery/mock/mock_project/早期介入/交付预案/输出结果/项目责任矩阵.xlsx
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1335,7 +1335,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1598,7 +1598,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -1894,7 +1894,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -2469,7 +2469,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -2506,7 +2506,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -2584,7 +2584,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
